--- a/virtual-physics-lab/app/dl/DHS_Q1h_drag_dataset.xlsx
+++ b/virtual-physics-lab/app/dl/DHS_Q1h_drag_dataset.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +102,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -668,442 +673,442 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>0.025</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.00106</v>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.00206</v>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>0.075</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.003</v>
       </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.00389</v>
       </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.00477</v>
       </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.00554</v>
       </c>
-      <c r="C12" s="6" t="n"/>
+      <c r="C12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>0.175</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>0.00637</v>
       </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>0.00708</v>
       </c>
-      <c r="C14" s="6" t="n"/>
+      <c r="C14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>0.225</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>0.00778</v>
       </c>
-      <c r="C15" s="6" t="n"/>
+      <c r="C15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>0.00839</v>
       </c>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>0.275</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>0.00971</v>
       </c>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
         <v>0.325</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>0.01019</v>
       </c>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>0.01071</v>
       </c>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
         <v>0.375</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>0.01126</v>
       </c>
-      <c r="C21" s="6" t="n"/>
+      <c r="C21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>0.01166</v>
       </c>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
         <v>0.425</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>0.01193</v>
       </c>
-      <c r="C23" s="6" t="n"/>
+      <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>0.01242</v>
       </c>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
         <v>0.475</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>0.01279</v>
       </c>
-      <c r="C25" s="6" t="n"/>
+      <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>0.01334</v>
       </c>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
         <v>0.525</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>0.01365</v>
       </c>
-      <c r="C27" s="6" t="n"/>
+      <c r="C27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>0.014</v>
       </c>
-      <c r="C28" s="6" t="n"/>
+      <c r="C28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
         <v>0.575</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>0.01411</v>
       </c>
-      <c r="C29" s="6" t="n"/>
+      <c r="C29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>0.0146</v>
       </c>
-      <c r="C30" s="6" t="n"/>
+      <c r="C30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
         <v>0.625</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>0.01489</v>
       </c>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>0.0151</v>
       </c>
-      <c r="C32" s="6" t="n"/>
+      <c r="C32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
         <v>0.675</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>0.01549</v>
       </c>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>0.01573</v>
       </c>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
         <v>0.725</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>0.01578</v>
       </c>
-      <c r="C35" s="6" t="n"/>
+      <c r="C35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>0.01611</v>
       </c>
-      <c r="C36" s="6" t="n"/>
+      <c r="C36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
         <v>0.775</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="6" t="n">
         <v>0.01626</v>
       </c>
-      <c r="C37" s="6" t="n"/>
+      <c r="C37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="6" t="n">
         <v>0.01638</v>
       </c>
-      <c r="C38" s="6" t="n"/>
+      <c r="C38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
         <v>0.825</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="6" t="n">
         <v>0.01687</v>
       </c>
-      <c r="C39" s="6" t="n"/>
+      <c r="C39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
         <v>0.85</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>0.01703</v>
       </c>
-      <c r="C40" s="6" t="n"/>
+      <c r="C40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
         <v>0.875</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>0.01714</v>
       </c>
-      <c r="C41" s="6" t="n"/>
+      <c r="C41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="6" t="n">
         <v>0.0173</v>
       </c>
-      <c r="C42" s="6" t="n"/>
+      <c r="C42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
         <v>0.925</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="6" t="n">
         <v>0.01733</v>
       </c>
-      <c r="C43" s="6" t="n"/>
+      <c r="C43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
         <v>0.95</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="6" t="n">
         <v>0.0175</v>
       </c>
-      <c r="C44" s="6" t="n"/>
+      <c r="C44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>0.01778</v>
       </c>
-      <c r="C45" s="6" t="n"/>
+      <c r="C45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="6" t="n">
         <v>0.01776</v>
       </c>
-      <c r="C46" s="6" t="n"/>
+      <c r="C46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
         <v>1.025</v>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="6" t="n">
         <v>0.01783</v>
       </c>
-      <c r="C47" s="6" t="n"/>
+      <c r="C47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
         <v>1.05</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="6" t="n">
         <v>0.0178</v>
       </c>
-      <c r="C48" s="6" t="n"/>
+      <c r="C48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
         <v>1.075</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="6" t="n">
         <v>0.01817</v>
       </c>
-      <c r="C49" s="6" t="n"/>
+      <c r="C49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="6" t="n">
         <v>0.01809</v>
       </c>
-      <c r="C50" s="6" t="n"/>
+      <c r="C50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
         <v>1.125</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>0.01835</v>
       </c>
-      <c r="C51" s="6" t="n"/>
+      <c r="C51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
         <v>1.15</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="6" t="n">
         <v>0.01837</v>
       </c>
-      <c r="C52" s="6" t="n"/>
+      <c r="C52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
         <v>1.175</v>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="6" t="n">
         <v>0.01845</v>
       </c>
-      <c r="C53" s="6" t="n"/>
+      <c r="C53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="6" t="n">
         <v>0.01844</v>
       </c>
-      <c r="C54" s="6" t="n"/>
+      <c r="C54" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1177,23 +1182,23 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>IF(A7="","",(B6+B7)/2*(A7-A6))</f>
         <v/>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>energy dissipated (0 to 1.000 m)</t>
         </is>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>SUMIFS(C6:C54,A6:A54,"&lt;0.9999")</f>
         <v/>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>J</t>
         </is>
@@ -1203,10 +1208,10 @@
       <c r="A7" s="5" t="n">
         <v>0.025</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.00106</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>IF(A8="","",(B7+B8)/2*(A8-A7))</f>
         <v/>
       </c>
@@ -1215,10 +1220,10 @@
       <c r="A8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.00206</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>IF(A9="","",(B8+B9)/2*(A9-A8))</f>
         <v/>
       </c>
@@ -1227,10 +1232,10 @@
       <c r="A9" s="5" t="n">
         <v>0.075</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.003</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>IF(A10="","",(B9+B10)/2*(A10-A9))</f>
         <v/>
       </c>
@@ -1239,10 +1244,10 @@
       <c r="A10" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.00389</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>IF(A11="","",(B10+B11)/2*(A11-A10))</f>
         <v/>
       </c>
@@ -1251,10 +1256,10 @@
       <c r="A11" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.00477</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>IF(A12="","",(B11+B12)/2*(A12-A11))</f>
         <v/>
       </c>
@@ -1263,10 +1268,10 @@
       <c r="A12" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.00554</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>IF(A13="","",(B12+B13)/2*(A13-A12))</f>
         <v/>
       </c>
@@ -1275,10 +1280,10 @@
       <c r="A13" s="5" t="n">
         <v>0.175</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>0.00637</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <f>IF(A14="","",(B13+B14)/2*(A14-A13))</f>
         <v/>
       </c>
@@ -1287,10 +1292,10 @@
       <c r="A14" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>0.00708</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <f>IF(A15="","",(B14+B15)/2*(A15-A14))</f>
         <v/>
       </c>
@@ -1299,10 +1304,10 @@
       <c r="A15" s="5" t="n">
         <v>0.225</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>0.00778</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <f>IF(A16="","",(B15+B16)/2*(A16-A15))</f>
         <v/>
       </c>
@@ -1311,10 +1316,10 @@
       <c r="A16" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>0.00839</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <f>IF(A17="","",(B16+B17)/2*(A17-A16))</f>
         <v/>
       </c>
@@ -1323,10 +1328,10 @@
       <c r="A17" s="5" t="n">
         <v>0.275</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <f>IF(A18="","",(B17+B18)/2*(A18-A17))</f>
         <v/>
       </c>
@@ -1335,10 +1340,10 @@
       <c r="A18" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>0.00971</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <f>IF(A19="","",(B18+B19)/2*(A19-A18))</f>
         <v/>
       </c>
@@ -1347,10 +1352,10 @@
       <c r="A19" s="5" t="n">
         <v>0.325</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>0.01019</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <f>IF(A20="","",(B19+B20)/2*(A20-A19))</f>
         <v/>
       </c>
@@ -1359,10 +1364,10 @@
       <c r="A20" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>0.01071</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <f>IF(A21="","",(B20+B21)/2*(A21-A20))</f>
         <v/>
       </c>
@@ -1371,10 +1376,10 @@
       <c r="A21" s="5" t="n">
         <v>0.375</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>0.01126</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <f>IF(A22="","",(B21+B22)/2*(A22-A21))</f>
         <v/>
       </c>
@@ -1383,10 +1388,10 @@
       <c r="A22" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>0.01166</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <f>IF(A23="","",(B22+B23)/2*(A23-A22))</f>
         <v/>
       </c>
@@ -1395,10 +1400,10 @@
       <c r="A23" s="5" t="n">
         <v>0.425</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>0.01193</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <f>IF(A24="","",(B23+B24)/2*(A24-A23))</f>
         <v/>
       </c>
@@ -1407,10 +1412,10 @@
       <c r="A24" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>0.01242</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <f>IF(A25="","",(B24+B25)/2*(A25-A24))</f>
         <v/>
       </c>
@@ -1419,10 +1424,10 @@
       <c r="A25" s="5" t="n">
         <v>0.475</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>0.01279</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <f>IF(A26="","",(B25+B26)/2*(A26-A25))</f>
         <v/>
       </c>
@@ -1431,10 +1436,10 @@
       <c r="A26" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>0.01334</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <f>IF(A27="","",(B26+B27)/2*(A27-A26))</f>
         <v/>
       </c>
@@ -1443,10 +1448,10 @@
       <c r="A27" s="5" t="n">
         <v>0.525</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>0.01365</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <f>IF(A28="","",(B27+B28)/2*(A28-A27))</f>
         <v/>
       </c>
@@ -1455,10 +1460,10 @@
       <c r="A28" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>0.014</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <f>IF(A29="","",(B28+B29)/2*(A29-A28))</f>
         <v/>
       </c>
@@ -1467,10 +1472,10 @@
       <c r="A29" s="5" t="n">
         <v>0.575</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>0.01411</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <f>IF(A30="","",(B29+B30)/2*(A30-A29))</f>
         <v/>
       </c>
@@ -1479,10 +1484,10 @@
       <c r="A30" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>0.0146</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="8">
         <f>IF(A31="","",(B30+B31)/2*(A31-A30))</f>
         <v/>
       </c>
@@ -1491,10 +1496,10 @@
       <c r="A31" s="5" t="n">
         <v>0.625</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>0.01489</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <f>IF(A32="","",(B31+B32)/2*(A32-A31))</f>
         <v/>
       </c>
@@ -1503,10 +1508,10 @@
       <c r="A32" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>0.0151</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="8">
         <f>IF(A33="","",(B32+B33)/2*(A33-A32))</f>
         <v/>
       </c>
@@ -1515,10 +1520,10 @@
       <c r="A33" s="5" t="n">
         <v>0.675</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>0.01549</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="8">
         <f>IF(A34="","",(B33+B34)/2*(A34-A33))</f>
         <v/>
       </c>
@@ -1527,10 +1532,10 @@
       <c r="A34" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>0.01573</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="8">
         <f>IF(A35="","",(B34+B35)/2*(A35-A34))</f>
         <v/>
       </c>
@@ -1539,10 +1544,10 @@
       <c r="A35" s="5" t="n">
         <v>0.725</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>0.01578</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="8">
         <f>IF(A36="","",(B35+B36)/2*(A36-A35))</f>
         <v/>
       </c>
@@ -1551,10 +1556,10 @@
       <c r="A36" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>0.01611</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="8">
         <f>IF(A37="","",(B36+B37)/2*(A37-A36))</f>
         <v/>
       </c>
@@ -1563,10 +1568,10 @@
       <c r="A37" s="5" t="n">
         <v>0.775</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="6" t="n">
         <v>0.01626</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="8">
         <f>IF(A38="","",(B37+B38)/2*(A38-A37))</f>
         <v/>
       </c>
@@ -1575,10 +1580,10 @@
       <c r="A38" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="6" t="n">
         <v>0.01638</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="8">
         <f>IF(A39="","",(B38+B39)/2*(A39-A38))</f>
         <v/>
       </c>
@@ -1587,10 +1592,10 @@
       <c r="A39" s="5" t="n">
         <v>0.825</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="6" t="n">
         <v>0.01687</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="8">
         <f>IF(A40="","",(B39+B40)/2*(A40-A39))</f>
         <v/>
       </c>
@@ -1599,10 +1604,10 @@
       <c r="A40" s="5" t="n">
         <v>0.85</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>0.01703</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="8">
         <f>IF(A41="","",(B40+B41)/2*(A41-A40))</f>
         <v/>
       </c>
@@ -1611,10 +1616,10 @@
       <c r="A41" s="5" t="n">
         <v>0.875</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>0.01714</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="8">
         <f>IF(A42="","",(B41+B42)/2*(A42-A41))</f>
         <v/>
       </c>
@@ -1623,10 +1628,10 @@
       <c r="A42" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="6" t="n">
         <v>0.0173</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="8">
         <f>IF(A43="","",(B42+B43)/2*(A43-A42))</f>
         <v/>
       </c>
@@ -1635,10 +1640,10 @@
       <c r="A43" s="5" t="n">
         <v>0.925</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="6" t="n">
         <v>0.01733</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="8">
         <f>IF(A44="","",(B43+B44)/2*(A44-A43))</f>
         <v/>
       </c>
@@ -1647,10 +1652,10 @@
       <c r="A44" s="5" t="n">
         <v>0.95</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="6" t="n">
         <v>0.0175</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="8">
         <f>IF(A45="","",(B44+B45)/2*(A45-A44))</f>
         <v/>
       </c>
@@ -1659,10 +1664,10 @@
       <c r="A45" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>0.01778</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="8">
         <f>IF(A46="","",(B45+B46)/2*(A46-A45))</f>
         <v/>
       </c>
@@ -1671,10 +1676,10 @@
       <c r="A46" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="6" t="n">
         <v>0.01776</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="8">
         <f>IF(A47="","",(B46+B47)/2*(A47-A46))</f>
         <v/>
       </c>
@@ -1683,10 +1688,10 @@
       <c r="A47" s="5" t="n">
         <v>1.025</v>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="6" t="n">
         <v>0.01783</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="8">
         <f>IF(A48="","",(B47+B48)/2*(A48-A47))</f>
         <v/>
       </c>
@@ -1695,10 +1700,10 @@
       <c r="A48" s="5" t="n">
         <v>1.05</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="6" t="n">
         <v>0.0178</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="8">
         <f>IF(A49="","",(B48+B49)/2*(A49-A48))</f>
         <v/>
       </c>
@@ -1707,10 +1712,10 @@
       <c r="A49" s="5" t="n">
         <v>1.075</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="6" t="n">
         <v>0.01817</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="8">
         <f>IF(A50="","",(B49+B50)/2*(A50-A49))</f>
         <v/>
       </c>
@@ -1719,10 +1724,10 @@
       <c r="A50" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="6" t="n">
         <v>0.01809</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="8">
         <f>IF(A51="","",(B50+B51)/2*(A51-A50))</f>
         <v/>
       </c>
@@ -1731,10 +1736,10 @@
       <c r="A51" s="5" t="n">
         <v>1.125</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>0.01835</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="8">
         <f>IF(A52="","",(B51+B52)/2*(A52-A51))</f>
         <v/>
       </c>
@@ -1743,10 +1748,10 @@
       <c r="A52" s="5" t="n">
         <v>1.15</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="6" t="n">
         <v>0.01837</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="8">
         <f>IF(A53="","",(B52+B53)/2*(A53-A52))</f>
         <v/>
       </c>
@@ -1755,10 +1760,10 @@
       <c r="A53" s="5" t="n">
         <v>1.175</v>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="6" t="n">
         <v>0.01845</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="8">
         <f>IF(A54="","",(B53+B54)/2*(A54-A53))</f>
         <v/>
       </c>
@@ -1767,10 +1772,10 @@
       <c r="A54" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="6" t="n">
         <v>0.01844</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="8">
         <f>IF(A55="","",(B54+B55)/2*(A55-A54))</f>
         <v/>
       </c>
